--- a/4 четверть_17_JavaScript_Electron.xlsx
+++ b/4 четверть_17_JavaScript_Electron.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8CEE285-C4C1-4E3F-9948-61409B2FBF2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636DB879-786F-43DE-979A-268245E22ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ElementUI" sheetId="35" r:id="rId1"/>
@@ -28,6 +28,8 @@
     <sheet name="session" sheetId="37" r:id="rId13"/>
     <sheet name="Os" sheetId="28" r:id="rId14"/>
     <sheet name="build" sheetId="31" r:id="rId15"/>
+    <sheet name="myexp Electron" sheetId="39" r:id="rId16"/>
+    <sheet name="myexp Updater" sheetId="40" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="1355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="1412">
   <si>
     <t>Пример</t>
   </si>
@@ -23122,17 +23124,1348 @@
   <si>
     <t>Vite + TypeScript</t>
   </si>
+  <si>
+    <t>electron</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Примечание 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Electron не умеет работать с проксированием путей к backend. Поэтому при сборке проекта необходимо обеспечить полный путь к каждому обработчику.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>npm run</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>electronbuilddev</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - собирает проект с установкой localhost в качестве основы полного пути
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">npm run electronbuildprod </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- собирает проект с установкой боевого адреса в качестве основы полного пути</t>
+    </r>
+  </si>
+  <si>
+    <t>electronbuilddev</t>
+  </si>
+  <si>
+    <t>VITE_ELECTRON_PROXY=1
+VITE_PAT_TO_BUILD= ./electron/renderer/dist/
+VITE_API_PROXY=http://127.0.0.1:9292
+VITE_SOCKET_PROXY=http://127.0.0.1:9092
+FILE_LOAD=https://mylk.hwcompany.ru</t>
+  </si>
+  <si>
+    <t>.env.electrondev</t>
+  </si>
+  <si>
+    <t>Переменные окружения</t>
+  </si>
+  <si>
+    <t>package</t>
+  </si>
+  <si>
+    <t>.env.electronprod</t>
+  </si>
+  <si>
+    <t>VITE_ELECTRON_PROXY=1
+VITE_PAT_TO_BUILD= ./electron/renderer/dist/
+VITE_API_PROXY=https://mylk.hwcompany.ru/api
+VITE_SOCKET_PROXY=https://mylk.hwcompany.ru</t>
+  </si>
+  <si>
+    <t>NODE_ENV=production
+VITE_API_PROXY='/api'
+VITE_PAT_TO_BUILD= /srv/deploy/sites/test/</t>
+  </si>
+  <si>
+    <t>.env.test</t>
+  </si>
+  <si>
+    <t>NODE_ENV=development
+VITE_LOCALPROXY=1
+VITE_API_PROXY=http://127.0.0.1:9292
+VITE_SOCKET_PROXY=http://127.0.0.1:9092
+VITE_FILE_LOAD=http://127.0.0.1:9292
+VITE_CHART_KEY=2mA4mpE-11E2B4G1B3J3B3A2C3F3B4E4D4uddD7E4F4lD3C4D2ac1wE3A3B2qH-8jB1C4B1qkiB4D1A33A15B12A4D7A2B4A4H4nj1b1A7A3KE3tpgA1C3A4C-16mD2FH3H1F-7B-22tC8B2E6D2E2F2I2C10A2D1D6C1G2D3r==</t>
+  </si>
+  <si>
+    <t>.env.development</t>
+  </si>
+  <si>
+    <t>NODE_ENV=production
+VITE_API_PROXY='/api'
+VITE_PAT_TO_BUILD=../../../srv/www/sites/mylk/</t>
+  </si>
+  <si>
+    <t>.env.production</t>
+  </si>
+  <si>
+    <t>"electronbuilddev": "vite build --mode electrondev",</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Примечание: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--mode — это встроенная возможность Vite, а не отдельная библиотека. Это стандартный CLI-флаг, который Vite предоставляет "из коробки". Он устанавливает режим (mode) сборки.</t>
+    </r>
+  </si>
+  <si>
+    <t>Доступ к переменным окружения в проекте</t>
+  </si>
+  <si>
+    <t>Часть 1</t>
+  </si>
+  <si>
+    <t>plugins/env.js</t>
+  </si>
+  <si>
+    <t>const EnvPlugin = {
+  install(Vue) {
+    Vue.prototype.$env = {
+      isLocalProxy: import.meta.env.VITE_LOCALPROXY,
+      isElectronProxy: import.meta.env.VITE_ELECTRON_PROXY,
+      pathToBuild: import.meta.env.VITE_PAT_TO_BUILD,
+      apiProxy: import.meta.env.VITE_API_PROXY,
+      socketProxy: import.meta.env.VITE_SOCKET_PROXY,
+      fileLoaderPath: import.meta.env.VITE_FILE_LOAD,
+    }
+  }
+}
+export default EnvPlugin</t>
+  </si>
+  <si>
+    <t>В остальных файлах</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>import Vue from "vue";</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+async getAllManagersFullNames(){
+            try {
+                this.loading = true;
+                const { body } = await this.$http.post(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vue.prototype.$env.apiProxy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + '/mailingsettings/getAllManagersFullNames', {})
+                if (body) {
+                    this.allManagersFullNames = body;
+                }
+            } finally {
+                this.loading = false;
+            }
+        },</t>
+    </r>
+  </si>
+  <si>
+    <t>Часть 2</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">scripts": {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    "dev": "vite --mode development",
+    "build": "export NODE_OPTIONS=--openssl-legacy-provider &amp;&amp; vite build --mode production",
+    "test": "export NODE_OPTIONS=--openssl-legacy-provider &amp;&amp; vite build --mode test",</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    "electronbuilddev": "vite build --mode electrondev",
+    "electronbuildprod": "vite build --mode electronprod",
+    "electron": "electron .",
+    "dist": "electron-builder --win --x64"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  },</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Примечание 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>npm run electron</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - позволяет запустить собранный vite проект в среде electron
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">npm run dist - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>собранный проект (состоит из html, css, js) собирает в дистрибутив exe</t>
+    </r>
+  </si>
+  <si>
+    <t>electron проект</t>
+  </si>
+  <si>
+    <t>electron/main</t>
+  </si>
+  <si>
+    <t>electron/preload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">import ElectronFLkFrontHwCApp from './application/index.mjs';
+new ElectronFLkFrontHwCApp();
+</t>
+  </si>
+  <si>
+    <t>import { app, BrowserWindow, session } from 'electron'
+import { fileURLToPath } from 'url';
+import { dirname, join  } from 'path';
+import squirrelStartup from 'electron-squirrel-startup';
+import { createRequire } from 'module';
+const require = createRequire(import.meta.url);
+const { autoUpdater } = require('electron-updater');
+const __filename = fileURLToPath(import.meta.url);
+const __dirname = dirname(__filename);
+export default class ElectronFLkFrontHwCApp {
+    window; 
+    constructor() {
+        if(squirrelStartup) app.quit();
+        this.setupAutoUpdater();
+        this.subscribeForAppEvents();
+        app.whenReady().then(()=&gt; {
+          session.defaultSession.clearStorageData();
+          this.createWindow();
+        });
+    }
+    createWindow() {
+        this.window = new BrowserWindow({
+            title: "some name",
+            width: 1400,
+            height: 800,
+            webPreferences: {
+              nodeIntegration: true,
+              contextIsolation: true,
+              webSecurity: false,
+              preload: join(__dirname, '..','..', 'preload', 'index.mjs')
+            }
+        });
+        this.window.loadFile(join(__dirname, '..','..', 'renderer', 'dist', 'index.html'))
+            .then(() =&gt; {
+              autoUpdater.checkForUpdates().then((isElectronAutoUpdaterOn) =&gt; {
+                if (isElectronAutoUpdaterOn) {
+                  this.showMessage("Checking for updates...", this.window)
+                  autoUpdater.checkForUpdates()
+                } else {
+                  this.showMessage("", this.window);
+                }
+              })
+            });
+        // this.window.webContents.openDevTools({mode:'detach'});
+        // this.window.webContents.openDevTools();
+        this.window.on('closed', () =&gt; {
+            this.window = null;
+        });
+    };
+    subscribeForAppEvents() {
+        app.on('window-all-closed', () =&gt; {
+          if (process.platform !== 'darwin') {
+            app.quit();
+          }
+        });
+        app.on('activate', () =&gt; {
+          if (BrowserWindow.getAllWindows().length === 0) {
+            this.createWindow();
+          }
+        });
+    };</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    setupAutoUpdater() {
+      autoUpdater.autoDownload = false;
+      autoUpdater.autoInstallOnAppQuit = true;
+      autoUpdater.on("update-available", (info) =&gt; {
+        this.showMessage("Update available", this.window);
+        autoUpdater.downloadUpdate();
+      });
+      autoUpdater.on("update-not-available", () =&gt; {
+        this.showMessage("No update available", this.window);
+      });
+      autoUpdater.on("update-downloaded", () =&gt; {
+        this.showMessage("Update downloaded", this.window);
+      });
+      autoUpdater.on("error", (err) =&gt; {
+        this.showMessage("Update error: " + err.message, this.window);
+      });
+    }
+    showMessage(message, window) {
+      window.webContents.send("updateMessage", message);
+    };
+}</t>
+  </si>
+  <si>
+    <t>electron/main/index.mjs</t>
+  </si>
+  <si>
+    <t>electron/main/application/index.mjs</t>
+  </si>
+  <si>
+    <t>electron/preload/index.mjs</t>
+  </si>
+  <si>
+    <t>// https://electronjs.org/docs/tutorial/security
+// Preload File that should be loaded into browser window instead of
+// setting nodeIntegration: true for browser window
+import { contextBridge, ipcRenderer } from 'electron'
+contextBridge.exposeInMainWorld('MessagesAPI', {
+  onLoaded: callback =&gt; {
+    ipcRenderer.on('loaded', callback)
+  }
+})
+contextBridge.exposeInMainWorld('bridge', {
+  updateMessage: callback =&gt; {
+    ipcRenderer.on('updateMessage', callback)
+  }
+})</t>
+  </si>
+  <si>
+    <r>
+      <t>electron/renderer/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dist</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пустая</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, но будет создана директория dist после отработки команды npm run dist</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dependencies
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"electron-squirrel-startup": "^1.0.1",
+"electron-updater": "^6.7.3",
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+devDependencies
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    "electron": "^39.2.7",
+    "electron-builder": "^26.4.0",</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const { createVuePlugin } = require('vite-plugin-vue2');
+import { defineConfig, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>loadEnv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> } from 'vite'
+import { nodePolyfills } from 'vite-plugin-node-polyfills';
+const path = require('path');
+import pluginRewriteAll from '@brrock/vite-plugin-rewrite-all';
+export default defineConfig(({ mode }) =&gt; {
+  // Загружаем переменные окружения
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  const env = loadEnv(mode, process.cwd(), '')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  const isLocalProxy = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>env.VITE_LOCALPROXY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> === '1';
+ return {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  base: env.VITE_ELECTRON_PROXY ? './' : '/',
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  plugins: [
+    createVuePlugin(),
+      pluginRewriteAll(),
+    nodePolyfills({ //ТРЕБУЕТСЯ для node.js модулей, встроенных в сторнние зависимости
+      globals: true,
+    })
+  ],
+  css: {
+    preprocessorOptions: {
+      scss: { silenceDeprecations: ['legacy-js-api', 'global-builtin','function-units','slash-div','import'] }
+    }
+  },
+  optimizeDeps: {
+    include: [
+      'lodash/debounce', 
+      'echarts/lib/echarts',
+    ]
+  },
+  build: {
+    outDir: env.VITE_PAT_TO_BUILD || 'dist',
+    assetsInlineLimit: 4096,
+  },
+  resolve: {
+    alias: {
+        'assets': path.resolve(__dirname, './src/assets'),
+        'components': path.resolve(__dirname, './src/components'),
+        'src': path.resolve(__dirname, './src'),
+        'vue': 'vue/dist/vue.esm.js',
+        '@': path.resolve(__dirname, './src'),
+        'sounds': path.resolve(__dirname, './public/sounds'),
+    }
+  },
+  server: isLocalProxy ? {
+      proxy: {
+        '/socket.io': {
+          target: env.VITE_SOCKET_PROXY,
+          ws: true
+        },
+        // '/exports': {
+        //    target: 'https://mylk.hwcompany.ru/',
+        //    secure: false,
+        //    changeOrigin: true
+        // }
+      },
+    } : {
+        port: 9390,
+        proxy: {
+            '/socket.io': {
+                ws: true
+            }
+        },
+        // historyApiFallback: true
+    },
+  };
+})
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">В vite package.json
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Важно! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  base: env.VITE_ELECTRON_PROXY ? './' : '/',
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> если правильно помню тут путь определяется относительно корневого index.html. В зависимости от того, где будет расположен index.html выбирается относительный или абсолютный путь навигации к остальным файлам собранного проекта</t>
+    </r>
+  </si>
+  <si>
+    <t>Updater</t>
+  </si>
+  <si>
+    <t>"electron-updater": "^6.7.3",</t>
+  </si>
+  <si>
+    <t>login.js</t>
+  </si>
+  <si>
+    <t>login.html</t>
+  </si>
+  <si>
+    <t>Слушаем процесс электрон и выводим сообщения</t>
+  </si>
+  <si>
+    <t>Front</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    if (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>window.bridge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> != null) {
+      window.bridge.updateMessage((event, message)=&gt;{;
+         </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> this.electronMessage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = message;
+      });
+    };</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;div&gt;{{ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>electronMessage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> }}&lt;/div&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Слушаем процесс электрон и передаем на front</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">contextBridge.exposeInMainWorld('bridge', {
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>updateMessage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: callback =&gt; {
+    ipcRenderer.on('</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>updateMessage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>', callback)
+  }
+})</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">createWindow() {
+        this.window = new BrowserWindow({
+            title: "some name",
+            width: 1400,
+            height: 800,
+            webPreferences: {
+              nodeIntegration: true,
+              contextIsolation: true,
+              webSecurity: false,
+              preload: join(__dirname, '..','..', 'preload', 'index.mjs')
+            }
+        });
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>this.window.loadFile(join(__dirname, '..','..', 'renderer', 'dist', 'index.html'))
+            .then(() =&gt; {
+              autoUpdater.checkForUpdates().then((isElectronAutoUpdaterOn) =&gt; {
+                if (isElectronAutoUpdaterOn) {
+                  this.showMessage("Checking for updates...", this.window)
+                  autoUpdater.checkForUpdates()
+                } else {
+                  this.showMessage("", this.window);
+                }
+              })
+            });</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+        // this.window.webContents.openDevTools({mode:'detach'});
+        // this.window.webContents.openDevTools();
+        this.window.on('closed', () =&gt; {
+            this.window = null;
+        });
+    };</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    setupAutoUpdater() {
+      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>autoUpdater</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.autoDownload = false;
+      autoUpdater.autoInstallOnAppQuit = true;
+      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>autoUpdater</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.on("update-available", (info) =&gt; {
+        this.showMessage("Update available", this.window);
+        autoUpdater.downloadUpdate();
+      });
+      autoUpdater.on("update-not-available", () =&gt; {
+        this.showMessage("No update available", this.window);
+      });
+      autoUpdater.on("update-downloaded", () =&gt; {
+        this.showMessage("Update downloaded", this.window);
+      });
+      autoUpdater.on("error", (err) =&gt; {
+        this.showMessage("Update error: " + err.message, this.window);
+      });
+    }
+    showMessage(message, window) {
+      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>window.webContents.send("updateMessage", message);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    };</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    constructor() {
+        if(squirrelStartup) app.quit();
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    this.setupAutoUpdater();</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+        this.subscribeForAppEvents();
+        app.whenReady().then(()=&gt; {
+          session.defaultSession.clearStorageData();
+          this.createWindow();
+        });
+    }</t>
+    </r>
+  </si>
+  <si>
+    <t>const { autoUpdater } = require('electron-updater');</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>repository</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": "https://github.com/GreatNameUser/LK_autoupdater",
+  "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>publish</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": {
+    "provider": "github",
+    "release": "release"
+  },
+  "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>build</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": {
+    "appId": "com.headway.lk",
+    "productName": "Headway LK",
+    "win": {
+      "target": "nsis",
+      "icon": "./public/img/icons/android-chrome-256x256.png"
+    },
+    "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>directories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": {
+      "output": "dist"
+    }
+  },</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Важно! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Любой дистрибутив необходимо сохранить заменив все пробелы в названии точками</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Только в этом случае autoupdater сможет распарсить его версию итд на github</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="58" x14ac:knownFonts="1">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -23820,9 +25153,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -23833,41 +25166,77 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -23879,31 +25248,16 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -23915,43 +25269,22 @@
     <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -23960,32 +25293,32 @@
     <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="55" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="56" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -23997,11 +25330,11 @@
     <xf numFmtId="49" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -24010,112 +25343,79 @@
     <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24124,55 +25424,106 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7B23FFB3-A72F-409B-B670-C03B7A66220A}"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -24312,6 +25663,55 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>164189</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1510478</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>5105400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71B3029A-4F37-4602-9241-3C0B17F159EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10995475" y="22097999"/>
+          <a:ext cx="1346289" cy="5050972"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -45684,6 +47084,4425 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B747A11D-0E73-46A9-A18A-5096740DA60C}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:U105"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="57.109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B2" s="10"/>
+      <c r="C2" s="9"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="U3" s="5"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C4" s="118" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="S4" s="2"/>
+      <c r="T4"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="26" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="S5" s="2"/>
+      <c r="T5"/>
+    </row>
+    <row r="6" spans="1:21" s="7" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="11"/>
+      <c r="B6" s="119" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C6" s="119" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D6" s="119" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="2"/>
+    </row>
+    <row r="7" spans="1:21" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="11"/>
+      <c r="B7" s="119" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="2"/>
+    </row>
+    <row r="8" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="120" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B8" s="119"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="2"/>
+    </row>
+    <row r="9" spans="1:21" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="119" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="2"/>
+    </row>
+    <row r="10" spans="1:21" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="119"/>
+      <c r="B10" s="119" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C10" s="119" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D10" s="119" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="2"/>
+    </row>
+    <row r="11" spans="1:21" s="7" customFormat="1" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="119" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="2"/>
+    </row>
+    <row r="12" spans="1:21" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="119" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B12" s="119" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="2"/>
+    </row>
+    <row r="13" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="120" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="2"/>
+    </row>
+    <row r="14" spans="1:21" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="119" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C14" s="119" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="2"/>
+    </row>
+    <row r="15" spans="1:21" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15" s="119" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B15" s="119" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C15" s="119" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="2"/>
+    </row>
+    <row r="16" spans="1:21" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="119" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="119" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="2"/>
+    </row>
+    <row r="17" spans="1:21" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="119" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="119" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="2"/>
+    </row>
+    <row r="18" spans="1:21" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="119" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="119" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="2"/>
+    </row>
+    <row r="19" spans="1:21" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="119" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="119" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="2"/>
+    </row>
+    <row r="20" spans="1:21" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="120" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B20" s="119" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C20" s="119"/>
+      <c r="D20" s="11"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="2"/>
+    </row>
+    <row r="21" spans="1:21" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="119" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="119" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="2"/>
+    </row>
+    <row r="22" spans="1:21" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="120" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B22" s="119" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="2"/>
+    </row>
+    <row r="23" spans="1:21" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="119" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C23" s="119" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D23" s="11"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="2"/>
+    </row>
+    <row r="24" spans="1:21" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="119" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C24" s="119" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="2"/>
+    </row>
+    <row r="25" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="2"/>
+    </row>
+    <row r="26" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="2"/>
+    </row>
+    <row r="27" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="2"/>
+    </row>
+    <row r="28" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="2"/>
+    </row>
+    <row r="29" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="2"/>
+    </row>
+    <row r="30" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="2"/>
+    </row>
+    <row r="31" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="2"/>
+    </row>
+    <row r="32" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="8"/>
+      <c r="U32" s="2"/>
+    </row>
+    <row r="33" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="2"/>
+    </row>
+    <row r="34" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="8"/>
+      <c r="U34" s="2"/>
+    </row>
+    <row r="35" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="2"/>
+    </row>
+    <row r="36" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="8"/>
+      <c r="U36" s="2"/>
+    </row>
+    <row r="37" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="8"/>
+      <c r="U37" s="2"/>
+    </row>
+    <row r="38" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="8"/>
+      <c r="U38" s="2"/>
+    </row>
+    <row r="39" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="2"/>
+    </row>
+    <row r="40" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="2"/>
+    </row>
+    <row r="41" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="2"/>
+    </row>
+    <row r="42" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="2"/>
+    </row>
+    <row r="43" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="8"/>
+      <c r="U43" s="2"/>
+    </row>
+    <row r="44" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="2"/>
+    </row>
+    <row r="45" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="11"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="8"/>
+      <c r="U45" s="2"/>
+    </row>
+    <row r="46" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="11"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="2"/>
+    </row>
+    <row r="47" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="11"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="8"/>
+      <c r="U47" s="2"/>
+    </row>
+    <row r="48" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="11"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="8"/>
+      <c r="U48" s="2"/>
+    </row>
+    <row r="49" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="11"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="8"/>
+      <c r="U49" s="2"/>
+    </row>
+    <row r="50" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="11"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="8"/>
+      <c r="U50" s="2"/>
+    </row>
+    <row r="51" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="11"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="8"/>
+      <c r="U51" s="2"/>
+    </row>
+    <row r="52" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="11"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="8"/>
+      <c r="U52" s="2"/>
+    </row>
+    <row r="53" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="11"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="2"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="8"/>
+      <c r="U53" s="2"/>
+    </row>
+    <row r="54" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="11"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="8"/>
+      <c r="U54" s="2"/>
+    </row>
+    <row r="55" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="1"/>
+      <c r="T55" s="8"/>
+      <c r="U55" s="2"/>
+    </row>
+    <row r="56" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="11"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="8"/>
+      <c r="U56" s="2"/>
+    </row>
+    <row r="57" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="8"/>
+      <c r="U57" s="2"/>
+    </row>
+    <row r="58" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="11"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="8"/>
+      <c r="U58" s="2"/>
+    </row>
+    <row r="59" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="2"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="8"/>
+      <c r="U59" s="2"/>
+    </row>
+    <row r="60" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="11"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="8"/>
+      <c r="U60" s="2"/>
+    </row>
+    <row r="61" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="11"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="1"/>
+      <c r="T61" s="8"/>
+      <c r="U61" s="2"/>
+    </row>
+    <row r="62" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="11"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="1"/>
+      <c r="T62" s="8"/>
+      <c r="U62" s="2"/>
+    </row>
+    <row r="63" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="11"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="1"/>
+      <c r="T63" s="8"/>
+      <c r="U63" s="2"/>
+    </row>
+    <row r="64" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="11"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="1"/>
+      <c r="T64" s="8"/>
+      <c r="U64" s="2"/>
+    </row>
+    <row r="65" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="11"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="1"/>
+      <c r="T65" s="8"/>
+      <c r="U65" s="2"/>
+    </row>
+    <row r="66" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="11"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="1"/>
+      <c r="T66" s="8"/>
+      <c r="U66" s="2"/>
+    </row>
+    <row r="67" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="11"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="1"/>
+      <c r="T67" s="8"/>
+      <c r="U67" s="2"/>
+    </row>
+    <row r="68" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="11"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="1"/>
+      <c r="T68" s="8"/>
+      <c r="U68" s="2"/>
+    </row>
+    <row r="69" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="11"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="2"/>
+      <c r="S69" s="1"/>
+      <c r="T69" s="8"/>
+      <c r="U69" s="2"/>
+    </row>
+    <row r="70" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="11"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="1"/>
+      <c r="T70" s="8"/>
+      <c r="U70" s="2"/>
+    </row>
+    <row r="71" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="11"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="1"/>
+      <c r="T71" s="8"/>
+      <c r="U71" s="2"/>
+    </row>
+    <row r="72" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="11"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="2"/>
+      <c r="S72" s="1"/>
+      <c r="T72" s="8"/>
+      <c r="U72" s="2"/>
+    </row>
+    <row r="73" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="11"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+      <c r="N73" s="1"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
+      <c r="R73" s="2"/>
+      <c r="S73" s="1"/>
+      <c r="T73" s="8"/>
+      <c r="U73" s="2"/>
+    </row>
+    <row r="74" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="11"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+      <c r="N74" s="1"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
+      <c r="R74" s="2"/>
+      <c r="S74" s="1"/>
+      <c r="T74" s="8"/>
+      <c r="U74" s="2"/>
+    </row>
+    <row r="75" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="11"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2"/>
+      <c r="R75" s="2"/>
+      <c r="S75" s="1"/>
+      <c r="T75" s="8"/>
+      <c r="U75" s="2"/>
+    </row>
+    <row r="76" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="11"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+      <c r="N76" s="1"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
+      <c r="R76" s="2"/>
+      <c r="S76" s="1"/>
+      <c r="T76" s="8"/>
+      <c r="U76" s="2"/>
+    </row>
+    <row r="77" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="11"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" s="2"/>
+      <c r="R77" s="2"/>
+      <c r="S77" s="1"/>
+      <c r="T77" s="8"/>
+      <c r="U77" s="2"/>
+    </row>
+    <row r="78" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="11"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+      <c r="P78" s="2"/>
+      <c r="Q78" s="2"/>
+      <c r="R78" s="2"/>
+      <c r="S78" s="1"/>
+      <c r="T78" s="8"/>
+      <c r="U78" s="2"/>
+    </row>
+    <row r="79" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="11"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1"/>
+      <c r="N79" s="1"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" s="2"/>
+      <c r="R79" s="2"/>
+      <c r="S79" s="1"/>
+      <c r="T79" s="8"/>
+      <c r="U79" s="2"/>
+    </row>
+    <row r="80" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="11"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1"/>
+      <c r="N80" s="1"/>
+      <c r="P80" s="2"/>
+      <c r="Q80" s="2"/>
+      <c r="R80" s="2"/>
+      <c r="S80" s="1"/>
+      <c r="T80" s="8"/>
+      <c r="U80" s="2"/>
+    </row>
+    <row r="81" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="11"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+      <c r="P81" s="2"/>
+      <c r="Q81" s="2"/>
+      <c r="R81" s="2"/>
+      <c r="S81" s="1"/>
+      <c r="T81" s="8"/>
+      <c r="U81" s="2"/>
+    </row>
+    <row r="82" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="11"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+      <c r="P82" s="2"/>
+      <c r="Q82" s="2"/>
+      <c r="R82" s="2"/>
+      <c r="S82" s="1"/>
+      <c r="T82" s="8"/>
+      <c r="U82" s="2"/>
+    </row>
+    <row r="83" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="11"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+      <c r="P83" s="2"/>
+      <c r="Q83" s="2"/>
+      <c r="R83" s="2"/>
+      <c r="S83" s="1"/>
+      <c r="T83" s="8"/>
+      <c r="U83" s="2"/>
+    </row>
+    <row r="84" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="11"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1"/>
+      <c r="N84" s="1"/>
+      <c r="P84" s="2"/>
+      <c r="Q84" s="2"/>
+      <c r="R84" s="2"/>
+      <c r="S84" s="1"/>
+      <c r="T84" s="8"/>
+      <c r="U84" s="2"/>
+    </row>
+    <row r="85" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="11"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1"/>
+      <c r="N85" s="1"/>
+      <c r="P85" s="2"/>
+      <c r="Q85" s="2"/>
+      <c r="R85" s="2"/>
+      <c r="S85" s="1"/>
+      <c r="T85" s="8"/>
+      <c r="U85" s="2"/>
+    </row>
+    <row r="86" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="11"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1"/>
+      <c r="N86" s="1"/>
+      <c r="P86" s="2"/>
+      <c r="Q86" s="2"/>
+      <c r="R86" s="2"/>
+      <c r="S86" s="1"/>
+      <c r="T86" s="8"/>
+      <c r="U86" s="2"/>
+    </row>
+    <row r="87" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="11"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1"/>
+      <c r="N87" s="1"/>
+      <c r="P87" s="2"/>
+      <c r="Q87" s="2"/>
+      <c r="R87" s="2"/>
+      <c r="S87" s="1"/>
+      <c r="T87" s="8"/>
+      <c r="U87" s="2"/>
+    </row>
+    <row r="88" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="11"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="11"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+      <c r="N88" s="1"/>
+      <c r="P88" s="2"/>
+      <c r="Q88" s="2"/>
+      <c r="R88" s="2"/>
+      <c r="S88" s="1"/>
+      <c r="T88" s="8"/>
+      <c r="U88" s="2"/>
+    </row>
+    <row r="89" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="11"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="1"/>
+      <c r="N89" s="1"/>
+      <c r="P89" s="2"/>
+      <c r="Q89" s="2"/>
+      <c r="R89" s="2"/>
+      <c r="S89" s="1"/>
+      <c r="T89" s="8"/>
+      <c r="U89" s="2"/>
+    </row>
+    <row r="90" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="11"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="11"/>
+      <c r="D90" s="11"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1"/>
+      <c r="N90" s="1"/>
+      <c r="P90" s="2"/>
+      <c r="Q90" s="2"/>
+      <c r="R90" s="2"/>
+      <c r="S90" s="1"/>
+      <c r="T90" s="8"/>
+      <c r="U90" s="2"/>
+    </row>
+    <row r="91" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="11"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1"/>
+      <c r="N91" s="1"/>
+      <c r="P91" s="2"/>
+      <c r="Q91" s="2"/>
+      <c r="R91" s="2"/>
+      <c r="S91" s="1"/>
+      <c r="T91" s="8"/>
+      <c r="U91" s="2"/>
+    </row>
+    <row r="92" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="11"/>
+      <c r="B92" s="11"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="11"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
+      <c r="N92" s="1"/>
+      <c r="P92" s="2"/>
+      <c r="Q92" s="2"/>
+      <c r="R92" s="2"/>
+      <c r="S92" s="1"/>
+      <c r="T92" s="8"/>
+      <c r="U92" s="2"/>
+    </row>
+    <row r="93" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="11"/>
+      <c r="B93" s="11"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+      <c r="N93" s="1"/>
+      <c r="P93" s="2"/>
+      <c r="Q93" s="2"/>
+      <c r="R93" s="2"/>
+      <c r="S93" s="1"/>
+      <c r="T93" s="8"/>
+      <c r="U93" s="2"/>
+    </row>
+    <row r="94" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="11"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="11"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="1"/>
+      <c r="N94" s="1"/>
+      <c r="P94" s="2"/>
+      <c r="Q94" s="2"/>
+      <c r="R94" s="2"/>
+      <c r="S94" s="1"/>
+      <c r="T94" s="8"/>
+      <c r="U94" s="2"/>
+    </row>
+    <row r="95" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="11"/>
+      <c r="B95" s="11"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="11"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1"/>
+      <c r="M95" s="1"/>
+      <c r="N95" s="1"/>
+      <c r="P95" s="2"/>
+      <c r="Q95" s="2"/>
+      <c r="R95" s="2"/>
+      <c r="S95" s="1"/>
+      <c r="T95" s="8"/>
+      <c r="U95" s="2"/>
+    </row>
+    <row r="96" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="11"/>
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="1"/>
+      <c r="N96" s="1"/>
+      <c r="P96" s="2"/>
+      <c r="Q96" s="2"/>
+      <c r="R96" s="2"/>
+      <c r="S96" s="1"/>
+      <c r="T96" s="8"/>
+      <c r="U96" s="2"/>
+    </row>
+    <row r="97" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="11"/>
+      <c r="B97" s="11"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="11"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
+      <c r="M97" s="1"/>
+      <c r="N97" s="1"/>
+      <c r="P97" s="2"/>
+      <c r="Q97" s="2"/>
+      <c r="R97" s="2"/>
+      <c r="S97" s="1"/>
+      <c r="T97" s="8"/>
+      <c r="U97" s="2"/>
+    </row>
+    <row r="98" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="11"/>
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="11"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="K98" s="1"/>
+      <c r="L98" s="1"/>
+      <c r="M98" s="1"/>
+      <c r="N98" s="1"/>
+      <c r="P98" s="2"/>
+      <c r="Q98" s="2"/>
+      <c r="R98" s="2"/>
+      <c r="S98" s="1"/>
+      <c r="T98" s="8"/>
+      <c r="U98" s="2"/>
+    </row>
+    <row r="99" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="11"/>
+      <c r="B99" s="11"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="11"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="K99" s="1"/>
+      <c r="L99" s="1"/>
+      <c r="M99" s="1"/>
+      <c r="N99" s="1"/>
+      <c r="P99" s="2"/>
+      <c r="Q99" s="2"/>
+      <c r="R99" s="2"/>
+      <c r="S99" s="1"/>
+      <c r="T99" s="8"/>
+      <c r="U99" s="2"/>
+    </row>
+    <row r="100" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="11"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="11"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+      <c r="N100" s="1"/>
+      <c r="P100" s="2"/>
+      <c r="Q100" s="2"/>
+      <c r="R100" s="2"/>
+      <c r="S100" s="1"/>
+      <c r="T100" s="8"/>
+      <c r="U100" s="2"/>
+    </row>
+    <row r="101" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="11"/>
+      <c r="B101" s="11"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="11"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1"/>
+      <c r="N101" s="1"/>
+      <c r="P101" s="2"/>
+      <c r="Q101" s="2"/>
+      <c r="R101" s="2"/>
+      <c r="S101" s="1"/>
+      <c r="T101" s="8"/>
+      <c r="U101" s="2"/>
+    </row>
+    <row r="102" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="11"/>
+      <c r="B102" s="11"/>
+      <c r="C102" s="11"/>
+      <c r="D102" s="11"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="K102" s="1"/>
+      <c r="L102" s="1"/>
+      <c r="M102" s="1"/>
+      <c r="N102" s="1"/>
+      <c r="P102" s="2"/>
+      <c r="Q102" s="2"/>
+      <c r="R102" s="2"/>
+      <c r="S102" s="1"/>
+      <c r="T102" s="8"/>
+      <c r="U102" s="2"/>
+    </row>
+    <row r="103" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="11"/>
+      <c r="B103" s="11"/>
+      <c r="C103" s="11"/>
+      <c r="D103" s="11"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="K103" s="1"/>
+      <c r="L103" s="1"/>
+      <c r="M103" s="1"/>
+      <c r="N103" s="1"/>
+      <c r="P103" s="2"/>
+      <c r="Q103" s="2"/>
+      <c r="R103" s="2"/>
+      <c r="S103" s="1"/>
+      <c r="T103" s="8"/>
+      <c r="U103" s="2"/>
+    </row>
+    <row r="104" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="11"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="11"/>
+      <c r="D104" s="11"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="K104" s="1"/>
+      <c r="L104" s="1"/>
+      <c r="M104" s="1"/>
+      <c r="N104" s="1"/>
+      <c r="P104" s="2"/>
+      <c r="Q104" s="2"/>
+      <c r="R104" s="2"/>
+      <c r="S104" s="1"/>
+      <c r="T104" s="8"/>
+      <c r="U104" s="2"/>
+    </row>
+    <row r="105" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="11"/>
+      <c r="B105" s="11"/>
+      <c r="C105" s="11"/>
+      <c r="D105" s="11"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="K105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1"/>
+      <c r="N105" s="1"/>
+      <c r="P105" s="2"/>
+      <c r="Q105" s="2"/>
+      <c r="R105" s="2"/>
+      <c r="S105" s="1"/>
+      <c r="T105" s="8"/>
+      <c r="U105" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7086A7-FB20-47D2-87D6-3B3F43D47C21}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:U112"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="57.109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B2" s="10"/>
+      <c r="C2" s="9"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="U3" s="5"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C4" s="118" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="S4" s="2"/>
+      <c r="T4"/>
+    </row>
+    <row r="5" spans="1:21" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="121"/>
+      <c r="B5" s="119" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D5" s="119" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="S5" s="2"/>
+      <c r="T5"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="120" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="S6" s="2"/>
+      <c r="T6"/>
+    </row>
+    <row r="7" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="123" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B7" s="29"/>
+      <c r="C7" s="119" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="2"/>
+    </row>
+    <row r="8" spans="1:21" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="123" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B8" s="119" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C8" s="119" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="2"/>
+    </row>
+    <row r="9" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="120" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="2"/>
+    </row>
+    <row r="10" spans="1:21" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" s="121"/>
+      <c r="B10" s="119" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C10" s="119" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="2"/>
+    </row>
+    <row r="11" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="120" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="2"/>
+    </row>
+    <row r="12" spans="1:21" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="123" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B12" s="119" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C12" s="119" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D12" s="119" t="s">
+        <v>1409</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="2"/>
+    </row>
+    <row r="13" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="122"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="11"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="2"/>
+    </row>
+    <row r="14" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="121"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="2"/>
+    </row>
+    <row r="15" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="121"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="11"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="2"/>
+    </row>
+    <row r="16" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="2"/>
+    </row>
+    <row r="17" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="121"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="11"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="2"/>
+    </row>
+    <row r="18" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="122"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="2"/>
+    </row>
+    <row r="19" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="122"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="2"/>
+    </row>
+    <row r="20" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="122"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="2"/>
+    </row>
+    <row r="21" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="122"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="2"/>
+    </row>
+    <row r="22" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="122"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="2"/>
+    </row>
+    <row r="23" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="122"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="2"/>
+    </row>
+    <row r="24" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="2"/>
+    </row>
+    <row r="25" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="2"/>
+    </row>
+    <row r="26" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="2"/>
+    </row>
+    <row r="27" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="2"/>
+    </row>
+    <row r="28" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="2"/>
+    </row>
+    <row r="29" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="2"/>
+    </row>
+    <row r="30" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="2"/>
+    </row>
+    <row r="31" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="2"/>
+    </row>
+    <row r="32" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="8"/>
+      <c r="U32" s="2"/>
+    </row>
+    <row r="33" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="2"/>
+    </row>
+    <row r="34" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="8"/>
+      <c r="U34" s="2"/>
+    </row>
+    <row r="35" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="2"/>
+    </row>
+    <row r="36" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="8"/>
+      <c r="U36" s="2"/>
+    </row>
+    <row r="37" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="8"/>
+      <c r="U37" s="2"/>
+    </row>
+    <row r="38" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="8"/>
+      <c r="U38" s="2"/>
+    </row>
+    <row r="39" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="2"/>
+    </row>
+    <row r="40" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="2"/>
+    </row>
+    <row r="41" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="2"/>
+    </row>
+    <row r="42" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="2"/>
+    </row>
+    <row r="43" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="8"/>
+      <c r="U43" s="2"/>
+    </row>
+    <row r="44" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="2"/>
+    </row>
+    <row r="45" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="11"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="8"/>
+      <c r="U45" s="2"/>
+    </row>
+    <row r="46" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="11"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="2"/>
+    </row>
+    <row r="47" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="11"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="8"/>
+      <c r="U47" s="2"/>
+    </row>
+    <row r="48" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="11"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="8"/>
+      <c r="U48" s="2"/>
+    </row>
+    <row r="49" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="11"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="8"/>
+      <c r="U49" s="2"/>
+    </row>
+    <row r="50" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="11"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="8"/>
+      <c r="U50" s="2"/>
+    </row>
+    <row r="51" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="11"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="8"/>
+      <c r="U51" s="2"/>
+    </row>
+    <row r="52" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="11"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="8"/>
+      <c r="U52" s="2"/>
+    </row>
+    <row r="53" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="11"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="2"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="8"/>
+      <c r="U53" s="2"/>
+    </row>
+    <row r="54" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="11"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="8"/>
+      <c r="U54" s="2"/>
+    </row>
+    <row r="55" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="1"/>
+      <c r="T55" s="8"/>
+      <c r="U55" s="2"/>
+    </row>
+    <row r="56" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="11"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="8"/>
+      <c r="U56" s="2"/>
+    </row>
+    <row r="57" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="8"/>
+      <c r="U57" s="2"/>
+    </row>
+    <row r="58" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="11"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="8"/>
+      <c r="U58" s="2"/>
+    </row>
+    <row r="59" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="2"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="8"/>
+      <c r="U59" s="2"/>
+    </row>
+    <row r="60" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="11"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="8"/>
+      <c r="U60" s="2"/>
+    </row>
+    <row r="61" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="11"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="1"/>
+      <c r="T61" s="8"/>
+      <c r="U61" s="2"/>
+    </row>
+    <row r="62" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="11"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="1"/>
+      <c r="T62" s="8"/>
+      <c r="U62" s="2"/>
+    </row>
+    <row r="63" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="11"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="1"/>
+      <c r="T63" s="8"/>
+      <c r="U63" s="2"/>
+    </row>
+    <row r="64" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="11"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="1"/>
+      <c r="T64" s="8"/>
+      <c r="U64" s="2"/>
+    </row>
+    <row r="65" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="11"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="1"/>
+      <c r="T65" s="8"/>
+      <c r="U65" s="2"/>
+    </row>
+    <row r="66" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="11"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="1"/>
+      <c r="T66" s="8"/>
+      <c r="U66" s="2"/>
+    </row>
+    <row r="67" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="11"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="1"/>
+      <c r="T67" s="8"/>
+      <c r="U67" s="2"/>
+    </row>
+    <row r="68" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="11"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="1"/>
+      <c r="T68" s="8"/>
+      <c r="U68" s="2"/>
+    </row>
+    <row r="69" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="11"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="2"/>
+      <c r="S69" s="1"/>
+      <c r="T69" s="8"/>
+      <c r="U69" s="2"/>
+    </row>
+    <row r="70" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="11"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="1"/>
+      <c r="T70" s="8"/>
+      <c r="U70" s="2"/>
+    </row>
+    <row r="71" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="11"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="1"/>
+      <c r="T71" s="8"/>
+      <c r="U71" s="2"/>
+    </row>
+    <row r="72" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="11"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="2"/>
+      <c r="S72" s="1"/>
+      <c r="T72" s="8"/>
+      <c r="U72" s="2"/>
+    </row>
+    <row r="73" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="11"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+      <c r="N73" s="1"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
+      <c r="R73" s="2"/>
+      <c r="S73" s="1"/>
+      <c r="T73" s="8"/>
+      <c r="U73" s="2"/>
+    </row>
+    <row r="74" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="11"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+      <c r="N74" s="1"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
+      <c r="R74" s="2"/>
+      <c r="S74" s="1"/>
+      <c r="T74" s="8"/>
+      <c r="U74" s="2"/>
+    </row>
+    <row r="75" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="11"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2"/>
+      <c r="R75" s="2"/>
+      <c r="S75" s="1"/>
+      <c r="T75" s="8"/>
+      <c r="U75" s="2"/>
+    </row>
+    <row r="76" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="11"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+      <c r="N76" s="1"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
+      <c r="R76" s="2"/>
+      <c r="S76" s="1"/>
+      <c r="T76" s="8"/>
+      <c r="U76" s="2"/>
+    </row>
+    <row r="77" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="11"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" s="2"/>
+      <c r="R77" s="2"/>
+      <c r="S77" s="1"/>
+      <c r="T77" s="8"/>
+      <c r="U77" s="2"/>
+    </row>
+    <row r="78" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="11"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+      <c r="P78" s="2"/>
+      <c r="Q78" s="2"/>
+      <c r="R78" s="2"/>
+      <c r="S78" s="1"/>
+      <c r="T78" s="8"/>
+      <c r="U78" s="2"/>
+    </row>
+    <row r="79" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="11"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1"/>
+      <c r="N79" s="1"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" s="2"/>
+      <c r="R79" s="2"/>
+      <c r="S79" s="1"/>
+      <c r="T79" s="8"/>
+      <c r="U79" s="2"/>
+    </row>
+    <row r="80" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="11"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1"/>
+      <c r="N80" s="1"/>
+      <c r="P80" s="2"/>
+      <c r="Q80" s="2"/>
+      <c r="R80" s="2"/>
+      <c r="S80" s="1"/>
+      <c r="T80" s="8"/>
+      <c r="U80" s="2"/>
+    </row>
+    <row r="81" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="11"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+      <c r="P81" s="2"/>
+      <c r="Q81" s="2"/>
+      <c r="R81" s="2"/>
+      <c r="S81" s="1"/>
+      <c r="T81" s="8"/>
+      <c r="U81" s="2"/>
+    </row>
+    <row r="82" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="11"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+      <c r="P82" s="2"/>
+      <c r="Q82" s="2"/>
+      <c r="R82" s="2"/>
+      <c r="S82" s="1"/>
+      <c r="T82" s="8"/>
+      <c r="U82" s="2"/>
+    </row>
+    <row r="83" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="11"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+      <c r="P83" s="2"/>
+      <c r="Q83" s="2"/>
+      <c r="R83" s="2"/>
+      <c r="S83" s="1"/>
+      <c r="T83" s="8"/>
+      <c r="U83" s="2"/>
+    </row>
+    <row r="84" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="11"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1"/>
+      <c r="N84" s="1"/>
+      <c r="P84" s="2"/>
+      <c r="Q84" s="2"/>
+      <c r="R84" s="2"/>
+      <c r="S84" s="1"/>
+      <c r="T84" s="8"/>
+      <c r="U84" s="2"/>
+    </row>
+    <row r="85" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="11"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1"/>
+      <c r="N85" s="1"/>
+      <c r="P85" s="2"/>
+      <c r="Q85" s="2"/>
+      <c r="R85" s="2"/>
+      <c r="S85" s="1"/>
+      <c r="T85" s="8"/>
+      <c r="U85" s="2"/>
+    </row>
+    <row r="86" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="11"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1"/>
+      <c r="N86" s="1"/>
+      <c r="P86" s="2"/>
+      <c r="Q86" s="2"/>
+      <c r="R86" s="2"/>
+      <c r="S86" s="1"/>
+      <c r="T86" s="8"/>
+      <c r="U86" s="2"/>
+    </row>
+    <row r="87" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="11"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1"/>
+      <c r="N87" s="1"/>
+      <c r="P87" s="2"/>
+      <c r="Q87" s="2"/>
+      <c r="R87" s="2"/>
+      <c r="S87" s="1"/>
+      <c r="T87" s="8"/>
+      <c r="U87" s="2"/>
+    </row>
+    <row r="88" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="11"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="11"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+      <c r="N88" s="1"/>
+      <c r="P88" s="2"/>
+      <c r="Q88" s="2"/>
+      <c r="R88" s="2"/>
+      <c r="S88" s="1"/>
+      <c r="T88" s="8"/>
+      <c r="U88" s="2"/>
+    </row>
+    <row r="89" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="11"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="1"/>
+      <c r="N89" s="1"/>
+      <c r="P89" s="2"/>
+      <c r="Q89" s="2"/>
+      <c r="R89" s="2"/>
+      <c r="S89" s="1"/>
+      <c r="T89" s="8"/>
+      <c r="U89" s="2"/>
+    </row>
+    <row r="90" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="11"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="11"/>
+      <c r="D90" s="11"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1"/>
+      <c r="N90" s="1"/>
+      <c r="P90" s="2"/>
+      <c r="Q90" s="2"/>
+      <c r="R90" s="2"/>
+      <c r="S90" s="1"/>
+      <c r="T90" s="8"/>
+      <c r="U90" s="2"/>
+    </row>
+    <row r="91" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="11"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1"/>
+      <c r="N91" s="1"/>
+      <c r="P91" s="2"/>
+      <c r="Q91" s="2"/>
+      <c r="R91" s="2"/>
+      <c r="S91" s="1"/>
+      <c r="T91" s="8"/>
+      <c r="U91" s="2"/>
+    </row>
+    <row r="92" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="11"/>
+      <c r="B92" s="11"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="11"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
+      <c r="N92" s="1"/>
+      <c r="P92" s="2"/>
+      <c r="Q92" s="2"/>
+      <c r="R92" s="2"/>
+      <c r="S92" s="1"/>
+      <c r="T92" s="8"/>
+      <c r="U92" s="2"/>
+    </row>
+    <row r="93" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="11"/>
+      <c r="B93" s="11"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+      <c r="N93" s="1"/>
+      <c r="P93" s="2"/>
+      <c r="Q93" s="2"/>
+      <c r="R93" s="2"/>
+      <c r="S93" s="1"/>
+      <c r="T93" s="8"/>
+      <c r="U93" s="2"/>
+    </row>
+    <row r="94" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="11"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="11"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="1"/>
+      <c r="N94" s="1"/>
+      <c r="P94" s="2"/>
+      <c r="Q94" s="2"/>
+      <c r="R94" s="2"/>
+      <c r="S94" s="1"/>
+      <c r="T94" s="8"/>
+      <c r="U94" s="2"/>
+    </row>
+    <row r="95" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="11"/>
+      <c r="B95" s="11"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="11"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1"/>
+      <c r="M95" s="1"/>
+      <c r="N95" s="1"/>
+      <c r="P95" s="2"/>
+      <c r="Q95" s="2"/>
+      <c r="R95" s="2"/>
+      <c r="S95" s="1"/>
+      <c r="T95" s="8"/>
+      <c r="U95" s="2"/>
+    </row>
+    <row r="96" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="11"/>
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="1"/>
+      <c r="N96" s="1"/>
+      <c r="P96" s="2"/>
+      <c r="Q96" s="2"/>
+      <c r="R96" s="2"/>
+      <c r="S96" s="1"/>
+      <c r="T96" s="8"/>
+      <c r="U96" s="2"/>
+    </row>
+    <row r="97" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="11"/>
+      <c r="B97" s="11"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="11"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
+      <c r="M97" s="1"/>
+      <c r="N97" s="1"/>
+      <c r="P97" s="2"/>
+      <c r="Q97" s="2"/>
+      <c r="R97" s="2"/>
+      <c r="S97" s="1"/>
+      <c r="T97" s="8"/>
+      <c r="U97" s="2"/>
+    </row>
+    <row r="98" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="11"/>
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="11"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="K98" s="1"/>
+      <c r="L98" s="1"/>
+      <c r="M98" s="1"/>
+      <c r="N98" s="1"/>
+      <c r="P98" s="2"/>
+      <c r="Q98" s="2"/>
+      <c r="R98" s="2"/>
+      <c r="S98" s="1"/>
+      <c r="T98" s="8"/>
+      <c r="U98" s="2"/>
+    </row>
+    <row r="99" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="11"/>
+      <c r="B99" s="11"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="11"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="K99" s="1"/>
+      <c r="L99" s="1"/>
+      <c r="M99" s="1"/>
+      <c r="N99" s="1"/>
+      <c r="P99" s="2"/>
+      <c r="Q99" s="2"/>
+      <c r="R99" s="2"/>
+      <c r="S99" s="1"/>
+      <c r="T99" s="8"/>
+      <c r="U99" s="2"/>
+    </row>
+    <row r="100" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="11"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="11"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+      <c r="N100" s="1"/>
+      <c r="P100" s="2"/>
+      <c r="Q100" s="2"/>
+      <c r="R100" s="2"/>
+      <c r="S100" s="1"/>
+      <c r="T100" s="8"/>
+      <c r="U100" s="2"/>
+    </row>
+    <row r="101" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="11"/>
+      <c r="B101" s="11"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="11"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1"/>
+      <c r="N101" s="1"/>
+      <c r="P101" s="2"/>
+      <c r="Q101" s="2"/>
+      <c r="R101" s="2"/>
+      <c r="S101" s="1"/>
+      <c r="T101" s="8"/>
+      <c r="U101" s="2"/>
+    </row>
+    <row r="102" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="11"/>
+      <c r="B102" s="11"/>
+      <c r="C102" s="11"/>
+      <c r="D102" s="11"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="K102" s="1"/>
+      <c r="L102" s="1"/>
+      <c r="M102" s="1"/>
+      <c r="N102" s="1"/>
+      <c r="P102" s="2"/>
+      <c r="Q102" s="2"/>
+      <c r="R102" s="2"/>
+      <c r="S102" s="1"/>
+      <c r="T102" s="8"/>
+      <c r="U102" s="2"/>
+    </row>
+    <row r="103" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="11"/>
+      <c r="B103" s="11"/>
+      <c r="C103" s="11"/>
+      <c r="D103" s="11"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="K103" s="1"/>
+      <c r="L103" s="1"/>
+      <c r="M103" s="1"/>
+      <c r="N103" s="1"/>
+      <c r="P103" s="2"/>
+      <c r="Q103" s="2"/>
+      <c r="R103" s="2"/>
+      <c r="S103" s="1"/>
+      <c r="T103" s="8"/>
+      <c r="U103" s="2"/>
+    </row>
+    <row r="104" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="11"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="11"/>
+      <c r="D104" s="11"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="K104" s="1"/>
+      <c r="L104" s="1"/>
+      <c r="M104" s="1"/>
+      <c r="N104" s="1"/>
+      <c r="P104" s="2"/>
+      <c r="Q104" s="2"/>
+      <c r="R104" s="2"/>
+      <c r="S104" s="1"/>
+      <c r="T104" s="8"/>
+      <c r="U104" s="2"/>
+    </row>
+    <row r="105" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="11"/>
+      <c r="B105" s="11"/>
+      <c r="C105" s="11"/>
+      <c r="D105" s="11"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="K105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1"/>
+      <c r="N105" s="1"/>
+      <c r="P105" s="2"/>
+      <c r="Q105" s="2"/>
+      <c r="R105" s="2"/>
+      <c r="S105" s="1"/>
+      <c r="T105" s="8"/>
+      <c r="U105" s="2"/>
+    </row>
+    <row r="106" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="11"/>
+      <c r="B106" s="11"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="11"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="K106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="1"/>
+      <c r="N106" s="1"/>
+      <c r="P106" s="2"/>
+      <c r="Q106" s="2"/>
+      <c r="R106" s="2"/>
+      <c r="S106" s="1"/>
+      <c r="T106" s="8"/>
+      <c r="U106" s="2"/>
+    </row>
+    <row r="107" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="11"/>
+      <c r="B107" s="11"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="11"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="K107" s="1"/>
+      <c r="L107" s="1"/>
+      <c r="M107" s="1"/>
+      <c r="N107" s="1"/>
+      <c r="P107" s="2"/>
+      <c r="Q107" s="2"/>
+      <c r="R107" s="2"/>
+      <c r="S107" s="1"/>
+      <c r="T107" s="8"/>
+      <c r="U107" s="2"/>
+    </row>
+    <row r="108" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="11"/>
+      <c r="B108" s="11"/>
+      <c r="C108" s="11"/>
+      <c r="D108" s="11"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="K108" s="1"/>
+      <c r="L108" s="1"/>
+      <c r="M108" s="1"/>
+      <c r="N108" s="1"/>
+      <c r="P108" s="2"/>
+      <c r="Q108" s="2"/>
+      <c r="R108" s="2"/>
+      <c r="S108" s="1"/>
+      <c r="T108" s="8"/>
+      <c r="U108" s="2"/>
+    </row>
+    <row r="109" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="11"/>
+      <c r="B109" s="11"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="11"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1"/>
+      <c r="N109" s="1"/>
+      <c r="P109" s="2"/>
+      <c r="Q109" s="2"/>
+      <c r="R109" s="2"/>
+      <c r="S109" s="1"/>
+      <c r="T109" s="8"/>
+      <c r="U109" s="2"/>
+    </row>
+    <row r="110" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="11"/>
+      <c r="B110" s="11"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="11"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="1"/>
+      <c r="N110" s="1"/>
+      <c r="P110" s="2"/>
+      <c r="Q110" s="2"/>
+      <c r="R110" s="2"/>
+      <c r="S110" s="1"/>
+      <c r="T110" s="8"/>
+      <c r="U110" s="2"/>
+    </row>
+    <row r="111" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="11"/>
+      <c r="B111" s="11"/>
+      <c r="C111" s="11"/>
+      <c r="D111" s="11"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
+      <c r="M111" s="1"/>
+      <c r="N111" s="1"/>
+      <c r="P111" s="2"/>
+      <c r="Q111" s="2"/>
+      <c r="R111" s="2"/>
+      <c r="S111" s="1"/>
+      <c r="T111" s="8"/>
+      <c r="U111" s="2"/>
+    </row>
+    <row r="112" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="11"/>
+      <c r="B112" s="11"/>
+      <c r="C112" s="11"/>
+      <c r="D112" s="11"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="K112" s="1"/>
+      <c r="L112" s="1"/>
+      <c r="M112" s="1"/>
+      <c r="N112" s="1"/>
+      <c r="P112" s="2"/>
+      <c r="Q112" s="2"/>
+      <c r="R112" s="2"/>
+      <c r="S112" s="1"/>
+      <c r="T112" s="8"/>
+      <c r="U112" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36E4AC98-238A-4AF7-9252-59602FEC73CC}">
   <sheetPr>

--- a/4 четверть_17_JavaScript_Electron.xlsx
+++ b/4 четверть_17_JavaScript_Electron.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636DB879-786F-43DE-979A-268245E22ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8968AF34-F991-4C22-957D-3D87DFC59C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7515" yWindow="-18705" windowWidth="23250" windowHeight="12450" firstSheet="8" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ElementUI" sheetId="35" r:id="rId1"/>
@@ -23222,9 +23222,6 @@
       </rPr>
       <t>- собирает проект с установкой боевого адреса в качестве основы полного пути</t>
     </r>
-  </si>
-  <si>
-    <t>electronbuilddev</t>
   </si>
   <si>
     <t>VITE_ELECTRON_PROXY=1
@@ -24447,17 +24444,28 @@
       <t>. Только в этом случае autoupdater сможет распарсить его версию итд на github</t>
     </r>
   </si>
+  <si>
+    <t>Файлы .env</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="60" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -25153,7 +25161,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -25166,41 +25174,77 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -25212,31 +25256,16 @@
     <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -25248,43 +25277,22 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -25293,32 +25301,32 @@
     <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="56" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="57" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -25330,11 +25338,11 @@
     <xf numFmtId="49" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -25343,112 +25351,79 @@
     <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -25457,67 +25432,100 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -25681,7 +25689,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1510478</xdr:colOff>
+      <xdr:colOff>1502858</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>5105400</xdr:rowOff>
     </xdr:to>
@@ -47157,7 +47165,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="29"/>
@@ -47173,10 +47181,10 @@
         <v>1356</v>
       </c>
       <c r="C6" s="119" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D6" s="119" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="2"/>
@@ -47196,7 +47204,7 @@
     <row r="7" spans="1:21" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="119" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
@@ -47217,7 +47225,7 @@
     </row>
     <row r="8" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="120" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B8" s="119"/>
       <c r="C8" s="11"/>
@@ -47239,11 +47247,11 @@
     </row>
     <row r="9" spans="1:21" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="119" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="B9" s="119"/>
       <c r="C9" s="119" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="D9" s="11"/>
       <c r="F9" s="1"/>
@@ -47264,13 +47272,13 @@
     <row r="10" spans="1:21" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A10" s="119"/>
       <c r="B10" s="119" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C10" s="119" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D10" s="119" t="s">
         <v>1385</v>
-      </c>
-      <c r="D10" s="119" t="s">
-        <v>1386</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="2"/>
@@ -47289,11 +47297,11 @@
     </row>
     <row r="11" spans="1:21" s="7" customFormat="1" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A11" s="119" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B11" s="119"/>
       <c r="C11" s="119" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="D11" s="11"/>
       <c r="F11" s="1"/>
@@ -47313,10 +47321,10 @@
     </row>
     <row r="12" spans="1:21" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="119" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B12" s="119" t="s">
         <v>1391</v>
-      </c>
-      <c r="B12" s="119" t="s">
-        <v>1392</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -47337,7 +47345,7 @@
     </row>
     <row r="13" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="120" t="s">
-        <v>1357</v>
+        <v>1411</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -47360,10 +47368,10 @@
     <row r="14" spans="1:21" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="11"/>
       <c r="B14" s="119" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C14" s="119" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D14" s="11"/>
       <c r="F14" s="1"/>
@@ -47383,13 +47391,13 @@
     </row>
     <row r="15" spans="1:21" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A15" s="119" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B15" s="119" t="s">
         <v>1359</v>
       </c>
-      <c r="B15" s="119" t="s">
-        <v>1360</v>
-      </c>
       <c r="C15" s="119" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D15" s="11"/>
       <c r="F15" s="1"/>
@@ -47409,11 +47417,11 @@
     </row>
     <row r="16" spans="1:21" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="119" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="119" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D16" s="11"/>
       <c r="F16" s="1"/>
@@ -47433,11 +47441,11 @@
     </row>
     <row r="17" spans="1:21" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="119" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="119" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D17" s="11"/>
       <c r="F17" s="1"/>
@@ -47457,11 +47465,11 @@
     </row>
     <row r="18" spans="1:21" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A18" s="119" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="119" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D18" s="11"/>
       <c r="F18" s="1"/>
@@ -47481,11 +47489,11 @@
     </row>
     <row r="19" spans="1:21" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="119" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="119" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D19" s="11"/>
       <c r="F19" s="1"/>
@@ -47505,10 +47513,10 @@
     </row>
     <row r="20" spans="1:21" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="120" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B20" s="119" t="s">
         <v>1372</v>
-      </c>
-      <c r="B20" s="119" t="s">
-        <v>1373</v>
       </c>
       <c r="C20" s="119"/>
       <c r="D20" s="11"/>
@@ -47529,11 +47537,11 @@
     </row>
     <row r="21" spans="1:21" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A21" s="119" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="119" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D21" s="11"/>
       <c r="F21" s="1"/>
@@ -47553,10 +47561,10 @@
     </row>
     <row r="22" spans="1:21" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="120" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="B22" s="119" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
@@ -47578,10 +47586,10 @@
     <row r="23" spans="1:21" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
       <c r="B23" s="119" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="C23" s="119" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D23" s="11"/>
       <c r="F23" s="1"/>
@@ -47602,10 +47610,10 @@
     <row r="24" spans="1:21" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
       <c r="B24" s="119" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C24" s="119" t="s">
         <v>1376</v>
-      </c>
-      <c r="C24" s="119" t="s">
-        <v>1377</v>
       </c>
       <c r="D24" s="11"/>
       <c r="F24" s="1"/>
@@ -49312,7 +49320,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="C4" s="118" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="D4" s="29"/>
       <c r="E4" s="1"/>
@@ -49324,13 +49332,13 @@
     <row r="5" spans="1:21" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A5" s="121"/>
       <c r="B5" s="119" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D5" s="119" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="E5" s="1"/>
       <c r="J5" s="1"/>
@@ -49340,7 +49348,7 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="120" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B6" s="29"/>
       <c r="C6" s="29"/>
@@ -49353,11 +49361,11 @@
     </row>
     <row r="7" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="123" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="B7" s="29"/>
       <c r="C7" s="119" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="D7" s="11"/>
       <c r="F7" s="1"/>
@@ -49377,13 +49385,13 @@
     </row>
     <row r="8" spans="1:21" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="123" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B8" s="119" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="D8" s="29"/>
       <c r="F8" s="1"/>
@@ -49403,7 +49411,7 @@
     </row>
     <row r="9" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="120" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -49426,10 +49434,10 @@
     <row r="10" spans="1:21" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="121"/>
       <c r="B10" s="119" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C10" s="119" t="s">
         <v>1404</v>
-      </c>
-      <c r="C10" s="119" t="s">
-        <v>1405</v>
       </c>
       <c r="D10" s="11"/>
       <c r="F10" s="1"/>
@@ -49449,7 +49457,7 @@
     </row>
     <row r="11" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="120" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -49471,16 +49479,16 @@
     </row>
     <row r="12" spans="1:21" s="7" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A12" s="123" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B12" s="119" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C12" s="119" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D12" s="119" t="s">
         <v>1408</v>
-      </c>
-      <c r="B12" s="119" t="s">
-        <v>1406</v>
-      </c>
-      <c r="C12" s="119" t="s">
-        <v>1407</v>
-      </c>
-      <c r="D12" s="119" t="s">
-        <v>1409</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="2"/>
@@ -51625,7 +51633,7 @@
       </c>
       <c r="D10" s="11"/>
     </row>
-    <row r="11" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12" t="s">
@@ -53353,7 +53361,7 @@
       </c>
       <c r="D13" s="85"/>
     </row>
-    <row r="14" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="85"/>
       <c r="B14" s="85"/>
       <c r="C14" s="85" t="s">
